--- a/data/trans_dic/P16A12-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,12</t>
+          <t>0,23; 1,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,23</t>
+          <t>0,22; 1,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,94</t>
+          <t>0,7; 2,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,39</t>
+          <t>0,49; 2,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,29</t>
+          <t>0,16; 1,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,91</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,3</t>
+          <t>0,84; 2,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,93</t>
+          <t>0,16; 0,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,0</t>
+          <t>0,92; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,14; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,43</t>
+          <t>0,6; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,29</t>
+          <t>0,96; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,93</t>
+          <t>0,32; 1,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,86</t>
+          <t>0,89; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,13</t>
+          <t>0,55; 2,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,88</t>
+          <t>0,44; 1,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,02</t>
+          <t>0,8; 1,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,82</t>
+          <t>0,71; 1,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,87</t>
+          <t>0,73; 1,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,14</t>
+          <t>0,89; 2,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,89</t>
+          <t>3,02; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,45</t>
+          <t>2,34; 5,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,64</t>
+          <t>3,76; 7,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,23</t>
+          <t>1,93; 7,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,22</t>
+          <t>2,1; 5,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,14</t>
+          <t>2,11; 5,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,81</t>
+          <t>2,05; 4,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,98</t>
+          <t>1,96; 3,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,2</t>
+          <t>2,74; 5,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,81</t>
+          <t>2,53; 4,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,78</t>
+          <t>3,24; 5,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,96</t>
+          <t>2,34; 5,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,76</t>
+          <t>9,18; 16,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,98</t>
+          <t>8,66; 15,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 15,89</t>
+          <t>9,64; 16,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 15,46</t>
+          <t>10,18; 15,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,29</t>
+          <t>7,28; 13,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,79; 15,14</t>
+          <t>8,96; 14,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,62</t>
+          <t>8,85; 14,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,32</t>
+          <t>5,28; 8,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,88</t>
+          <t>9,06; 13,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,5; 13,78</t>
+          <t>9,57; 14,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,53</t>
+          <t>10,04; 14,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,54</t>
+          <t>8,37; 11,3</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,28; 24,22</t>
+          <t>15,49; 24,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,73; 34,84</t>
+          <t>24,11; 35,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,49; 32,53</t>
+          <t>22,25; 32,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,67; 24,08</t>
+          <t>17,68; 24,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,4; 25,19</t>
+          <t>16,84; 24,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,46; 28,42</t>
+          <t>19,54; 28,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,26; 26,9</t>
+          <t>18,38; 27,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,76</t>
+          <t>4,57; 16,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,48; 23,28</t>
+          <t>17,37; 23,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,95; 30,21</t>
+          <t>23,03; 30,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,65; 27,76</t>
+          <t>21,41; 27,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 19,09</t>
+          <t>7,9; 19,21</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,85; 25,61</t>
+          <t>15,04; 25,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,18; 35,32</t>
+          <t>22,67; 34,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,24; 38,52</t>
+          <t>28,27; 38,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,18; 32,47</t>
+          <t>23,97; 32,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,06; 25,12</t>
+          <t>16,11; 24,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,57; 34,91</t>
+          <t>25,98; 35,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,24; 31,45</t>
+          <t>21,6; 31,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,66; 32,68</t>
+          <t>26,5; 32,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,93; 24,09</t>
+          <t>17,16; 24,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,4; 33,89</t>
+          <t>26,39; 34,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,74; 32,93</t>
+          <t>25,87; 33,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,64; 31,75</t>
+          <t>26,59; 31,52</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,39</t>
+          <t>4,86; 6,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,27</t>
+          <t>6,46; 8,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,33</t>
+          <t>7,45; 9,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,24</t>
+          <t>6,12; 9,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,02</t>
+          <t>5,29; 6,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,59; 9,45</t>
+          <t>7,52; 9,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,84</t>
+          <t>6,98; 8,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,66</t>
+          <t>5,68; 7,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,38</t>
+          <t>5,3; 6,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,6</t>
+          <t>7,22; 8,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,77</t>
+          <t>7,46; 8,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,28</t>
+          <t>6,48; 8,24</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>0; 4869</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6474</t>
+          <t>0; 6576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 5660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>985; 9083</t>
+          <t>992; 8039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5907</t>
+          <t>0; 5468</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5265</t>
+          <t>0; 4907</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1899; 10864</t>
+          <t>1912; 11444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 6202</t>
+          <t>0; 5823</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7168</t>
+          <t>0; 10411</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4843; 20194</t>
+          <t>4838; 19693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7028</t>
+          <t>0; 6976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10882</t>
+          <t>0; 7904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6405</t>
+          <t>0; 6469</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2927; 14532</t>
+          <t>2992; 15500</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>879; 7271</t>
+          <t>881; 7510</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4166</t>
+          <t>0; 3940</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>892; 12401</t>
+          <t>889; 11925</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11396; 29844</t>
+          <t>10822; 30321</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1820; 10769</t>
+          <t>1849; 10547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 10803</t>
+          <t>0; 12040</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5764; 19112</t>
+          <t>5850; 19161</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>920; 8989</t>
+          <t>932; 9606</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4063; 16284</t>
+          <t>4016; 15709</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5338; 17625</t>
+          <t>5138; 17686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2212; 13332</t>
+          <t>2197; 13043</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6120; 20155</t>
+          <t>6268; 20297</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3616; 14098</t>
+          <t>3626; 14122</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2409; 10195</t>
+          <t>2378; 9672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10389; 26829</t>
+          <t>10650; 25967</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9208; 25243</t>
+          <t>9781; 25374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9520; 24854</t>
+          <t>9703; 25212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9050; 23078</t>
+          <t>9611; 23889</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14872; 35758</t>
+          <t>15664; 36587</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13690; 33505</t>
+          <t>14354; 33080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25514; 49376</t>
+          <t>24299; 49604</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18651; 64226</t>
+          <t>17139; 65338</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10110; 26918</t>
+          <t>10847; 26505</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13000; 31577</t>
+          <t>12961; 32681</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12898; 31237</t>
+          <t>13287; 31588</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14080; 28391</t>
+          <t>13966; 27793</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27947; 53761</t>
+          <t>28361; 54744</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32637; 59148</t>
+          <t>31112; 58762</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42690; 74870</t>
+          <t>41984; 73404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35144; 79317</t>
+          <t>37427; 81605</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35874; 60956</t>
+          <t>35519; 62562</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36871; 64160</t>
+          <t>37112; 64561</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47149; 75962</t>
+          <t>46058; 77821</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57760; 86626</t>
+          <t>57014; 87409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30172; 53699</t>
+          <t>29405; 55047</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39355; 67797</t>
+          <t>40143; 66286</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42774; 72636</t>
+          <t>43954; 74135</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28055; 45330</t>
+          <t>28753; 45056</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72218; 109746</t>
+          <t>71620; 106325</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83265; 120766</t>
+          <t>83809; 124648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98262; 141620</t>
+          <t>97872; 138445</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91742; 127490</t>
+          <t>92514; 124923</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44698; 70865</t>
+          <t>45316; 71941</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73502; 107919</t>
+          <t>74678; 108809</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75200; 108754</t>
+          <t>74372; 107890</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65070; 88649</t>
+          <t>65096; 90877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56230; 86371</t>
+          <t>57761; 85401</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68871; 100589</t>
+          <t>69180; 101498</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68996; 101629</t>
+          <t>69440; 103076</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27920; 101951</t>
+          <t>27779; 102099</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111097; 147966</t>
+          <t>110393; 149360</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>152310; 200546</t>
+          <t>152875; 199696</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>154198; 197681</t>
+          <t>152450; 198801</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>78219; 186466</t>
+          <t>77131; 187610</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31167; 53753</t>
+          <t>31574; 53989</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57735; 87966</t>
+          <t>56455; 87079</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72571; 98984</t>
+          <t>72663; 100211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68381; 91802</t>
+          <t>67778; 92137</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53614; 83871</t>
+          <t>53800; 82660</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98880; 135017</t>
+          <t>100497; 137185</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84993; 125861</t>
+          <t>86437; 127941</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>113251; 138811</t>
+          <t>112567; 138026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>92057; 130980</t>
+          <t>93298; 131671</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>167835; 215459</t>
+          <t>167809; 216222</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>169171; 216410</t>
+          <t>170010; 217809</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>188488; 224599</t>
+          <t>188118; 222992</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>158970; 209442</t>
+          <t>159289; 209717</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>219446; 282832</t>
+          <t>221138; 284347</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>253157; 316850</t>
+          <t>252972; 316276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>222751; 319679</t>
+          <t>211549; 319523</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>177613; 237097</t>
+          <t>178922; 234057</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>269319; 335355</t>
+          <t>266721; 333511</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>246106; 313433</t>
+          <t>247421; 316075</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>203062; 280081</t>
+          <t>207611; 281874</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>349023; 424353</t>
+          <t>352733; 426803</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>502682; 599412</t>
+          <t>502880; 592595</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>517317; 608821</t>
+          <t>517427; 610129</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>470477; 588927</t>
+          <t>461231; 586496</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A12-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,87</t>
+          <t>0,23; 1,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,3</t>
+          <t>0,21; 1,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,54</t>
+          <t>0,5; 2,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,88</t>
+          <t>0,06; 0,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,34</t>
+          <t>0,78; 2,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,91</t>
+          <t>0,16; 0,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,0</t>
+          <t>1,0; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,15; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,35</t>
+          <t>0,59; 2,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,3</t>
+          <t>1,02; 3,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,89</t>
+          <t>0,32; 1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,88</t>
+          <t>0,97; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,14</t>
+          <t>0,43; 2,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,78</t>
+          <t>0,57; 2,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,96</t>
+          <t>0,8; 2,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,83</t>
+          <t>0,67; 1,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,89</t>
+          <t>0,72; 1,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,21</t>
+          <t>0,98; 2,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,05</t>
+          <t>2,84; 6,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,38</t>
+          <t>2,35; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,68</t>
+          <t>3,82; 7,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,36</t>
+          <t>4,85; 8,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,14</t>
+          <t>1,98; 5,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,32</t>
+          <t>2,19; 5,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,87</t>
+          <t>1,97; 4,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,9</t>
+          <t>2,1; 4,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,29</t>
+          <t>2,81; 5,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,78</t>
+          <t>2,62; 4,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,67</t>
+          <t>3,3; 5,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,1</t>
+          <t>3,58; 5,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 16,18</t>
+          <t>9,28; 15,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 15,07</t>
+          <t>8,75; 15,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 16,28</t>
+          <t>9,82; 16,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,6</t>
+          <t>10,33; 15,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 13,63</t>
+          <t>7,54; 13,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 14,8</t>
+          <t>8,77; 15,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 14,92</t>
+          <t>8,97; 14,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,27</t>
+          <t>5,21; 8,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,45</t>
+          <t>8,94; 13,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 14,23</t>
+          <t>9,48; 13,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,2</t>
+          <t>10,0; 14,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,37; 11,3</t>
+          <t>8,24; 11,22</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,49; 24,59</t>
+          <t>15,63; 24,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,11; 35,12</t>
+          <t>23,44; 35,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,25; 32,27</t>
+          <t>22,24; 32,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,68; 24,68</t>
+          <t>16,67; 23,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,84; 24,9</t>
+          <t>16,82; 25,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,54; 28,67</t>
+          <t>19,59; 28,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,38; 27,29</t>
+          <t>17,75; 26,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,78</t>
+          <t>13,65; 18,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,5</t>
+          <t>17,22; 23,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,03; 30,08</t>
+          <t>22,96; 29,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,41; 27,92</t>
+          <t>21,29; 28,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,9; 19,21</t>
+          <t>15,97; 19,98</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,04; 25,72</t>
+          <t>14,94; 25,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 34,97</t>
+          <t>23,15; 35,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,27; 38,99</t>
+          <t>28,08; 39,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,97; 32,58</t>
+          <t>23,89; 32,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 24,76</t>
+          <t>16,0; 25,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,98; 35,47</t>
+          <t>25,68; 35,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,6; 31,97</t>
+          <t>21,64; 32,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,5; 32,5</t>
+          <t>26,58; 32,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,16; 24,21</t>
+          <t>16,92; 23,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,39; 34,01</t>
+          <t>26,3; 33,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 33,14</t>
+          <t>25,43; 32,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,59; 31,52</t>
+          <t>26,29; 31,1</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,4</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,31</t>
+          <t>6,37; 8,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,32</t>
+          <t>7,44; 9,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,24</t>
+          <t>7,86; 9,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,93</t>
+          <t>5,24; 6,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 9,4</t>
+          <t>7,53; 9,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,92</t>
+          <t>6,92; 8,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,68; 7,71</t>
+          <t>6,83; 8,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,41</t>
+          <t>5,3; 6,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,5</t>
+          <t>7,27; 8,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,79</t>
+          <t>7,46; 8,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,24</t>
+          <t>7,51; 8,6</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 5357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6576</t>
+          <t>0; 6538</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5660</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>992; 8039</t>
+          <t>990; 8110</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,27 +2103,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5468</t>
+          <t>0; 6332</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 5870</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1912; 11444</t>
+          <t>1893; 10949</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 4674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5823</t>
+          <t>0; 6080</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>776</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2664</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10411</t>
+          <t>0; 8917</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4838; 19693</t>
+          <t>4834; 19723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6976</t>
+          <t>0; 7066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7904</t>
+          <t>0; 9688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6469</t>
+          <t>0; 8201</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2992; 15500</t>
+          <t>3031; 15587</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>881; 7510</t>
+          <t>880; 7467</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 4655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>889; 11925</t>
+          <t>883; 12271</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10822; 30321</t>
+          <t>10122; 28118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1849; 10547</t>
+          <t>1870; 11196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 12040</t>
+          <t>0; 11080</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>19433</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5850; 19161</t>
+          <t>6393; 18950</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>932; 9606</t>
+          <t>1034; 9956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4016; 15709</t>
+          <t>3917; 17578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5138; 17686</t>
+          <t>6321; 20335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2197; 13043</t>
+          <t>2191; 12450</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6268; 20297</t>
+          <t>6865; 20363</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3626; 14122</t>
+          <t>2867; 13440</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2378; 9672</t>
+          <t>3561; 12545</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10650; 25967</t>
+          <t>10585; 26986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9781; 25374</t>
+          <t>9223; 24982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9703; 25212</t>
+          <t>9618; 24409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9611; 23889</t>
+          <t>12123; 28745</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>66605</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15664; 36587</t>
+          <t>14738; 34965</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14354; 33080</t>
+          <t>14459; 33578</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24299; 49604</t>
+          <t>24700; 49687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17139; 65338</t>
+          <t>34009; 60929</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10847; 26505</t>
+          <t>10202; 26813</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12961; 32681</t>
+          <t>13449; 32943</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13287; 31588</t>
+          <t>12786; 31217</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13966; 27793</t>
+          <t>15462; 30025</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28361; 54744</t>
+          <t>29037; 53937</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31112; 58762</t>
+          <t>32167; 59801</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41984; 73404</t>
+          <t>42741; 74290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37427; 81605</t>
+          <t>51489; 82603</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71811</t>
+          <t>77926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36169</t>
+          <t>40734</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>107980</t>
+          <t>118660</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35519; 62562</t>
+          <t>35883; 60467</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37112; 64561</t>
+          <t>37495; 64791</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46058; 77821</t>
+          <t>46912; 77502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57014; 87409</t>
+          <t>62854; 93150</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29405; 55047</t>
+          <t>30465; 53672</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40143; 66286</t>
+          <t>39292; 67612</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43954; 74135</t>
+          <t>44581; 73630</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28753; 45056</t>
+          <t>31638; 50646</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71620; 106325</t>
+          <t>70657; 105579</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83809; 124648</t>
+          <t>83061; 120834</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97872; 138445</t>
+          <t>97461; 141090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92514; 124923</t>
+          <t>100220; 136471</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>81937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>70186</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>141611</t>
+          <t>152123</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45316; 71941</t>
+          <t>45734; 70623</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74678; 108809</t>
+          <t>72600; 108965</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74372; 107890</t>
+          <t>74341; 107036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65096; 90877</t>
+          <t>67875; 96821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57761; 85401</t>
+          <t>57688; 86776</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69180; 101498</t>
+          <t>69363; 101062</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69440; 103076</t>
+          <t>67041; 100759</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27779; 102099</t>
+          <t>59946; 81474</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110393; 149360</t>
+          <t>109464; 148197</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>152875; 199696</t>
+          <t>152386; 199028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>152450; 198801</t>
+          <t>151634; 199411</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>77131; 187610</t>
+          <t>135108; 169043</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79761</t>
+          <t>86954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>125946</t>
+          <t>135858</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>205706</t>
+          <t>222813</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31574; 53989</t>
+          <t>31361; 53671</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56455; 87079</t>
+          <t>57648; 87209</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72663; 100211</t>
+          <t>72158; 100270</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67778; 92137</t>
+          <t>74101; 100196</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53800; 82660</t>
+          <t>53418; 84769</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>100497; 137185</t>
+          <t>99329; 138344</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86437; 127941</t>
+          <t>86591; 128166</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>112567; 138026</t>
+          <t>123194; 151135</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>93298; 131671</t>
+          <t>91992; 130154</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>167809; 216222</t>
+          <t>167190; 216002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170010; 217809</t>
+          <t>167149; 216765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>188118; 222992</t>
+          <t>203362; 240605</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>277246</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>535825</t>
+          <t>583403</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>159289; 209717</t>
+          <t>158228; 209691</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>221138; 284347</t>
+          <t>218039; 282352</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>252972; 316276</t>
+          <t>252521; 313703</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>211549; 319523</t>
+          <t>277521; 339357</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>178922; 234057</t>
+          <t>177006; 231537</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>266721; 333511</t>
+          <t>267237; 332385</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>247421; 316075</t>
+          <t>245451; 315598</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>207611; 281874</t>
+          <t>254897; 304505</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>352733; 426803</t>
+          <t>352579; 428694</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>502880; 592595</t>
+          <t>506456; 597037</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>517427; 610129</t>
+          <t>517451; 605904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>461231; 586496</t>
+          <t>545388; 624473</t>
         </is>
       </c>
     </row>
